--- a/output/2026-09-16_02_Croazia_Brodsko-posavska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-16_02_Croazia_Brodsko-posavska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore/rappresentante autorizzato macchinari industriali (compressori CompAir/Champion, pompe vuoto e soffianti Elmo Rietschle/Robuschi/Nash/Wittig anche ATEX, generatori azoto/ossigeno Inmatec, attrezzature industriali/cantiere); vendita, noleggio, assistenza. Secondo numero fonte originale (035 404 310) non riscontrato singolarmente.</t>
+          <t>Rivenditore/rappresentante autorizzato macchinari industriali (compressori CompAir/Champion, pompe vuoto e soffianti Elmo Rietschle/Robuschi/Nash/Wittig anche ATEX, generatori azoto/ossigeno Inmatec, attrezzature industriali/cantiere); vendita, noleggio, assistenza. Secondo numero fonte originale (035 404 310) non riscontrato singolarmente. [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
